--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165925</v>
       </c>
       <c r="B2" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165515</v>
       </c>
       <c r="B3" t="n">
-        <v>98573</v>
+        <v>98576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165381</v>
+        <v>129165479</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685227</v>
+        <v>685218</v>
       </c>
       <c r="R4" t="n">
-        <v>7088607</v>
+        <v>7088841</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165479</v>
+        <v>129165381</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685218</v>
+        <v>685227</v>
       </c>
       <c r="R5" t="n">
-        <v>7088841</v>
+        <v>7088607</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>129165935</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129165433</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129165340</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129165341</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129165480</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129165926</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129165385</v>
       </c>
       <c r="B13" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129166214</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129165353</v>
       </c>
       <c r="B15" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129165934</v>
+        <v>129165339</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>78793</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685231</v>
+        <v>684948</v>
       </c>
       <c r="R17" t="n">
-        <v>7088866</v>
+        <v>7088680</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129165339</v>
+        <v>129165934</v>
       </c>
       <c r="B18" t="n">
-        <v>78792</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684948</v>
+        <v>685231</v>
       </c>
       <c r="R18" t="n">
-        <v>7088680</v>
+        <v>7088866</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2352,7 +2352,7 @@
         <v>129165382</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165479</v>
+        <v>129165381</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685218</v>
+        <v>685227</v>
       </c>
       <c r="R4" t="n">
-        <v>7088841</v>
+        <v>7088607</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165381</v>
+        <v>129165479</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685227</v>
+        <v>685218</v>
       </c>
       <c r="R5" t="n">
-        <v>7088607</v>
+        <v>7088841</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129165433</v>
+        <v>129165340</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685405</v>
+        <v>685200</v>
       </c>
       <c r="R7" t="n">
-        <v>7088626</v>
+        <v>7088594</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129165340</v>
+        <v>129165433</v>
       </c>
       <c r="B8" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685200</v>
+        <v>685405</v>
       </c>
       <c r="R8" t="n">
-        <v>7088594</v>
+        <v>7088626</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165341</v>
+        <v>129165480</v>
       </c>
       <c r="B9" t="n">
-        <v>78793</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685362</v>
+        <v>685182</v>
       </c>
       <c r="R9" t="n">
-        <v>7088640</v>
+        <v>7088834</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129165480</v>
+        <v>129165926</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685182</v>
+        <v>685234</v>
       </c>
       <c r="R10" t="n">
-        <v>7088834</v>
+        <v>7088894</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165926</v>
+        <v>129165341</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>78793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685234</v>
+        <v>685362</v>
       </c>
       <c r="R11" t="n">
-        <v>7088894</v>
+        <v>7088640</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129165339</v>
+        <v>129165934</v>
       </c>
       <c r="B17" t="n">
-        <v>78793</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684948</v>
+        <v>685231</v>
       </c>
       <c r="R17" t="n">
-        <v>7088680</v>
+        <v>7088866</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129165934</v>
+        <v>129165339</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>78793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685231</v>
+        <v>684948</v>
       </c>
       <c r="R18" t="n">
-        <v>7088866</v>
+        <v>7088680</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165381</v>
+        <v>129165479</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685227</v>
+        <v>685218</v>
       </c>
       <c r="R4" t="n">
-        <v>7088607</v>
+        <v>7088841</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165479</v>
+        <v>129165381</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685218</v>
+        <v>685227</v>
       </c>
       <c r="R5" t="n">
-        <v>7088841</v>
+        <v>7088607</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129165340</v>
+        <v>129165433</v>
       </c>
       <c r="B7" t="n">
-        <v>78793</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685200</v>
+        <v>685405</v>
       </c>
       <c r="R7" t="n">
-        <v>7088594</v>
+        <v>7088626</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129165433</v>
+        <v>129165340</v>
       </c>
       <c r="B8" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1278,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685405</v>
+        <v>685200</v>
       </c>
       <c r="R8" t="n">
-        <v>7088626</v>
+        <v>7088594</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165925</v>
       </c>
       <c r="B2" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165515</v>
       </c>
       <c r="B3" t="n">
-        <v>98576</v>
+        <v>98586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165479</v>
+        <v>129165381</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685218</v>
+        <v>685227</v>
       </c>
       <c r="R4" t="n">
-        <v>7088841</v>
+        <v>7088607</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -945,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165381</v>
+        <v>129165479</v>
       </c>
       <c r="B5" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685227</v>
+        <v>685218</v>
       </c>
       <c r="R5" t="n">
-        <v>7088607</v>
+        <v>7088841</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1047,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,7 +1076,7 @@
         <v>129165935</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129165433</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129165340</v>
       </c>
       <c r="B8" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165480</v>
+        <v>129165341</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>78797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685182</v>
+        <v>685362</v>
       </c>
       <c r="R9" t="n">
-        <v>7088834</v>
+        <v>7088640</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129165926</v>
+        <v>129165480</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685234</v>
+        <v>685182</v>
       </c>
       <c r="R10" t="n">
-        <v>7088894</v>
+        <v>7088834</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165341</v>
+        <v>129165926</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685362</v>
+        <v>685234</v>
       </c>
       <c r="R11" t="n">
-        <v>7088640</v>
+        <v>7088894</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1658,7 +1658,7 @@
         <v>129165247</v>
       </c>
       <c r="B12" t="n">
-        <v>56913</v>
+        <v>56915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129165385</v>
       </c>
       <c r="B13" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129166214</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129165353</v>
       </c>
       <c r="B15" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129165287</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>129165934</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>129165339</v>
       </c>
       <c r="B18" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>129165382</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165341</v>
+        <v>129165480</v>
       </c>
       <c r="B9" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685362</v>
+        <v>685182</v>
       </c>
       <c r="R9" t="n">
-        <v>7088640</v>
+        <v>7088834</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129165480</v>
+        <v>129165341</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685182</v>
+        <v>685362</v>
       </c>
       <c r="R10" t="n">
-        <v>7088834</v>
+        <v>7088640</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129165934</v>
+        <v>129165339</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>78797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685231</v>
+        <v>684948</v>
       </c>
       <c r="R17" t="n">
-        <v>7088866</v>
+        <v>7088680</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129165339</v>
+        <v>129165934</v>
       </c>
       <c r="B18" t="n">
-        <v>78797</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684948</v>
+        <v>685231</v>
       </c>
       <c r="R18" t="n">
-        <v>7088680</v>
+        <v>7088866</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129165515</v>
       </c>
       <c r="B3" t="n">
-        <v>98586</v>
+        <v>98593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129165381</v>
+        <v>129165479</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685227</v>
+        <v>685218</v>
       </c>
       <c r="R4" t="n">
-        <v>7088607</v>
+        <v>7088841</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -945,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129165479</v>
+        <v>129165381</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685218</v>
+        <v>685227</v>
       </c>
       <c r="R5" t="n">
-        <v>7088841</v>
+        <v>7088607</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1042,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165480</v>
+        <v>129165926</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685182</v>
+        <v>685234</v>
       </c>
       <c r="R9" t="n">
-        <v>7088834</v>
+        <v>7088894</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129165341</v>
+        <v>129165480</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685362</v>
+        <v>685182</v>
       </c>
       <c r="R10" t="n">
-        <v>7088640</v>
+        <v>7088834</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165926</v>
+        <v>129165341</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>78797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685234</v>
+        <v>685362</v>
       </c>
       <c r="R11" t="n">
-        <v>7088894</v>
+        <v>7088640</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129165925</v>
       </c>
       <c r="B2" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129165515</v>
       </c>
       <c r="B3" t="n">
-        <v>98593</v>
+        <v>98595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129165479</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129165381</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129165935</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129165433</v>
       </c>
       <c r="B7" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129165340</v>
       </c>
       <c r="B8" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129165926</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>129165480</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
         <v>129165341</v>
       </c>
       <c r="B11" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>129165247</v>
       </c>
       <c r="B12" t="n">
-        <v>56915</v>
+        <v>56917</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>129165385</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129166214</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>129165353</v>
       </c>
       <c r="B15" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>129165287</v>
       </c>
       <c r="B16" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129165339</v>
+        <v>129165934</v>
       </c>
       <c r="B17" t="n">
-        <v>78797</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684948</v>
+        <v>685231</v>
       </c>
       <c r="R17" t="n">
-        <v>7088680</v>
+        <v>7088866</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129165934</v>
+        <v>129165339</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>78799</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>685231</v>
+        <v>684948</v>
       </c>
       <c r="R18" t="n">
-        <v>7088866</v>
+        <v>7088680</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2352,7 +2352,7 @@
         <v>129165382</v>
       </c>
       <c r="B19" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165926</v>
+        <v>129165341</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685234</v>
+        <v>685362</v>
       </c>
       <c r="R9" t="n">
-        <v>7088894</v>
+        <v>7088640</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165341</v>
+        <v>129165926</v>
       </c>
       <c r="B11" t="n">
-        <v>78799</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685362</v>
+        <v>685234</v>
       </c>
       <c r="R11" t="n">
-        <v>7088640</v>
+        <v>7088894</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 7915-2022 artfynd.xlsx
+++ b/artfynd/A 7915-2022 artfynd.xlsx
@@ -1364,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129165341</v>
+        <v>129165480</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685362</v>
+        <v>685182</v>
       </c>
       <c r="R9" t="n">
-        <v>7088640</v>
+        <v>7088834</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129165480</v>
+        <v>129165926</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685182</v>
+        <v>685234</v>
       </c>
       <c r="R10" t="n">
-        <v>7088834</v>
+        <v>7088894</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
+          <t>2021-10-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-10-11</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129165926</v>
+        <v>129165341</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685234</v>
+        <v>685362</v>
       </c>
       <c r="R11" t="n">
-        <v>7088894</v>
+        <v>7088640</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-10-05</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2022-10-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
